--- a/data/trans_orig/P24B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23758</t>
+          <t>24489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45286</t>
+          <t>45003</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26730</t>
+          <t>26015</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38506</t>
+          <t>39217</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65825</t>
+          <t>63052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92478</t>
+          <t>91481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115441</t>
+          <t>114684</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46001</t>
+          <t>46162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63753</t>
+          <t>64544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>145495</t>
+          <t>146339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174961</t>
+          <t>174152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12267</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28022</t>
+          <t>27677</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22252</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44373</t>
+          <t>44375</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16942</t>
+          <t>15376</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34705</t>
+          <t>34893</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41041</t>
+          <t>41227</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43206</t>
+          <t>43437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69472</t>
+          <t>71250</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79603</t>
+          <t>79265</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101382</t>
+          <t>102075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>71795</t>
+          <t>72109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94187</t>
+          <t>94322</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>159873</t>
+          <t>157728</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>191053</t>
+          <t>189903</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>70,81%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29204</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29165</t>
+          <t>28394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26738</t>
+          <t>26365</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50295</t>
+          <t>49898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23299</t>
+          <t>24214</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44030</t>
+          <t>44955</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>20351</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35673</t>
+          <t>36030</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60891</t>
+          <t>60343</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170167</t>
+          <t>170050</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>198304</t>
+          <t>199119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17060</t>
+          <t>17180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29733</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192202</t>
+          <t>192826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223720</t>
+          <t>223817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,5%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25322</t>
+          <t>25751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47974</t>
+          <t>47999</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32907</t>
+          <t>33914</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58817</t>
+          <t>58479</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70507</t>
+          <t>70499</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103983</t>
+          <t>104292</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38328</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65389</t>
+          <t>65367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117024</t>
+          <t>115480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>159791</t>
+          <t>158322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>379997</t>
+          <t>378232</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>424079</t>
+          <t>424092</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123892</t>
+          <t>123621</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154694</t>
+          <t>155377</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>516266</t>
+          <t>513722</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569691</t>
+          <t>569037</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60010</t>
+          <t>59981</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>94484</t>
+          <t>93017</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>37714</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63473</t>
+          <t>63965</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106990</t>
+          <t>106713</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>147247</t>
+          <t>149159</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,51%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43579</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17715</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36501</t>
+          <t>37445</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43445</t>
+          <t>44227</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72079</t>
+          <t>72884</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>120972</t>
+          <t>120580</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>146259</t>
+          <t>146361</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>108508</t>
+          <t>107709</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>133054</t>
+          <t>132301</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>238075</t>
+          <t>237108</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>273146</t>
+          <t>273908</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,62%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30804</t>
+          <t>31577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23728</t>
+          <t>23460</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45053</t>
+          <t>45064</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41566</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69187</t>
+          <t>68216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13680</t>
+          <t>12710</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>14263</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30746</t>
+          <t>31274</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>39351</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,32%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>42897</t>
+          <t>43617</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61419</t>
+          <t>61326</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88563</t>
+          <t>90003</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114712</t>
+          <t>114551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>138633</t>
+          <t>138710</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170479</t>
+          <t>170713</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20636</t>
+          <t>19983</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>38723</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34635</t>
+          <t>33830</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57064</t>
+          <t>56042</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>59526</t>
+          <t>58891</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>89034</t>
+          <t>86512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>188548</t>
+          <t>189450</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>239569</t>
+          <t>244133</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>138690</t>
+          <t>135473</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>184435</t>
+          <t>183836</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>340787</t>
+          <t>340594</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>410688</t>
+          <t>413167</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>937079</t>
+          <t>941192</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1005973</t>
+          <t>1005927</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>496056</t>
+          <t>496802</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>553260</t>
+          <t>553683</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1452546</t>
+          <t>1451520</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1543138</t>
+          <t>1539884</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,68%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>167828</t>
+          <t>168086</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>219345</t>
+          <t>220344</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>152657</t>
+          <t>153789</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>199860</t>
+          <t>200599</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>336532</t>
+          <t>335761</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>408070</t>
+          <t>403272</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42355</t>
+          <t>42479</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66889</t>
+          <t>67371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22755</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42006</t>
+          <t>42271</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71024</t>
+          <t>68979</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101554</t>
+          <t>99942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63468</t>
+          <t>62618</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>88457</t>
+          <t>86910</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45232</t>
+          <t>43601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66191</t>
+          <t>64977</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,94%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114433</t>
+          <t>114719</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146352</t>
+          <t>147052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>11286</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28859</t>
+          <t>28925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>5909</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19978</t>
+          <t>19832</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20889</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43915</t>
+          <t>44401</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,96%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>31450</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57084</t>
+          <t>57045</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>27239</t>
+          <t>26021</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>48758</t>
+          <t>47053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65324</t>
+          <t>64773</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98684</t>
+          <t>97182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62479</t>
+          <t>61658</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88440</t>
+          <t>88354</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49223</t>
+          <t>48566</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73278</t>
+          <t>71977</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>117545</t>
+          <t>117676</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>153399</t>
+          <t>152301</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>55,15%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>21508</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43694</t>
+          <t>43176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18975</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39706</t>
+          <t>40042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46037</t>
+          <t>47230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>76084</t>
+          <t>79260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67474</t>
+          <t>69138</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>99405</t>
+          <t>101768</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35272</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91676</t>
+          <t>92856</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127739</t>
+          <t>129454</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,15%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126303</t>
+          <t>123866</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159808</t>
+          <t>159036</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38882</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56868</t>
+          <t>56796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169488</t>
+          <t>169826</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208833</t>
+          <t>208424</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,2%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35297</t>
+          <t>35892</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60190</t>
+          <t>60516</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>20861</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45401</t>
+          <t>45938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73541</t>
+          <t>74707</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>133083</t>
+          <t>132236</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>175238</t>
+          <t>173915</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64552</t>
+          <t>63357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96058</t>
+          <t>95014</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206074</t>
+          <t>206630</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>259673</t>
+          <t>257849</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,88%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258497</t>
+          <t>258720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>304084</t>
+          <t>303713</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>130923</t>
+          <t>131603</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>167190</t>
+          <t>165375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,47 +5689,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>57,85%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>430242</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>401593</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>458661</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>54,86%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>58,48%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>397</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>430242</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>400845</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>460234</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>54,86%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>51,11%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>58,68%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50541</t>
+          <t>50942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81385</t>
+          <t>81951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43439</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72577</t>
+          <t>71820</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>101645</t>
+          <t>102375</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>145152</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>44127</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>69673</t>
+          <t>70178</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42279</t>
+          <t>41791</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69093</t>
+          <t>67747</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>93719</t>
+          <t>91547</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>130345</t>
+          <t>129814</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>108921</t>
+          <t>108640</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>138828</t>
+          <t>137487</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>92788</t>
+          <t>93436</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>124035</t>
+          <t>123702</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>208474</t>
+          <t>209250</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>252120</t>
+          <t>251792</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>58,1%</t>
+          <t>58,03%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51191</t>
+          <t>50615</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40321</t>
+          <t>39687</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67197</t>
+          <t>65859</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74744</t>
+          <t>76454</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>109681</t>
+          <t>110149</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8657</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21188</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>42546</t>
+          <t>41296</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>32836</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>58431</t>
+          <t>56995</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40714</t>
+          <t>40863</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78700</t>
+          <t>75994</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103045</t>
+          <t>103653</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>46,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>107766</t>
+          <t>108153</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138765</t>
+          <t>139401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>61,48%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22228</t>
+          <t>23030</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33591</t>
+          <t>32524</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55259</t>
+          <t>55185</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>45820</t>
+          <t>46300</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73011</t>
+          <t>72984</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>375478</t>
+          <t>370298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>444587</t>
+          <t>443590</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>229905</t>
+          <t>230258</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>287591</t>
+          <t>287202</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>621339</t>
+          <t>618624</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>713264</t>
+          <t>710433</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>692278</t>
+          <t>693166</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>768978</t>
+          <t>770103</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>478150</t>
+          <t>475854</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>546310</t>
+          <t>543870</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1191524</t>
+          <t>1187922</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1290963</t>
+          <t>1289585</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,43%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>186185</t>
+          <t>190259</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>244909</t>
+          <t>245319</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>181683</t>
+          <t>182675</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>233608</t>
+          <t>234323</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>387019</t>
+          <t>382486</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>463754</t>
+          <t>459674</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,76%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016</t>
+          <t>Población según su autopercepción de si fuma más, menos o igual que hace dos años en 2016 (tasa de respuesta: 98,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36896</t>
+          <t>37685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24398</t>
+          <t>24837</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33350</t>
+          <t>33460</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57565</t>
+          <t>57227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58233</t>
+          <t>57291</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78897</t>
+          <t>78081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34367</t>
+          <t>34476</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49581</t>
+          <t>49432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97079</t>
+          <t>97985</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123450</t>
+          <t>123049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>71,98%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4714</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>2708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11755</t>
+          <t>11450</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>25215</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16003</t>
+          <t>15882</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33500</t>
+          <t>32423</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>15220</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>32487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35817</t>
+          <t>35150</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62020</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60726</t>
+          <t>61486</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79970</t>
+          <t>80908</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52069</t>
+          <t>52593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72386</t>
+          <t>71622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>53,08%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>117800</t>
+          <t>118826</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>147142</t>
+          <t>146351</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7934</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23218</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14880</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34942</t>
+          <t>35164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25524</t>
+          <t>25685</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47819</t>
+          <t>48456</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10144</t>
+          <t>9925</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23984</t>
+          <t>24055</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>40391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66364</t>
+          <t>65823</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136391</t>
+          <t>135010</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162711</t>
+          <t>163477</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19954</t>
+          <t>20164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>34934</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159266</t>
+          <t>160355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>192095</t>
+          <t>190137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20850</t>
+          <t>20129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40846</t>
+          <t>41957</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4515</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>15558</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27400</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52458</t>
+          <t>50432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86957</t>
+          <t>86414</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121548</t>
+          <t>121357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58700</t>
+          <t>58684</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88776</t>
+          <t>88906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>150794</t>
+          <t>155604</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198557</t>
+          <t>204326</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,53%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>256194</t>
+          <t>254979</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294014</t>
+          <t>295585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178906</t>
+          <t>178705</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214175</t>
+          <t>214199</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>448432</t>
+          <t>445651</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>501334</t>
+          <t>499503</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>36344</t>
+          <t>35416</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>63145</t>
+          <t>62335</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>32915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58381</t>
+          <t>58670</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74982</t>
+          <t>75051</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>111705</t>
+          <t>111965</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>43765</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70495</t>
+          <t>72586</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>30738</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52910</t>
+          <t>53602</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80322</t>
+          <t>80948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>116756</t>
+          <t>114188</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>140443</t>
+          <t>140219</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>171431</t>
+          <t>171604</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>137850</t>
+          <t>136720</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>165367</t>
+          <t>164270</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>285930</t>
+          <t>287596</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>326611</t>
+          <t>328433</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>72,11%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19650</t>
+          <t>19184</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>41150</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14342</t>
+          <t>14363</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32072</t>
+          <t>32266</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>37170</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65009</t>
+          <t>65690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>4428</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16425</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>38537</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27532</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>50381</t>
+          <t>49756</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40239</t>
+          <t>40644</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56211</t>
+          <t>56225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>102770</t>
+          <t>102733</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127991</t>
+          <t>127225</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147404</t>
+          <t>147749</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177707</t>
+          <t>177152</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>73,2%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8706</t>
+          <t>8276</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22250</t>
+          <t>21256</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>18537</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38551</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30475</t>
+          <t>30194</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53818</t>
+          <t>53302</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229757</t>
+          <t>228647</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>292075</t>
+          <t>287680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>175320</t>
+          <t>175165</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>225064</t>
+          <t>223493</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>416818</t>
+          <t>416563</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>493377</t>
+          <t>492024</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>734717</t>
+          <t>736715</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>801148</t>
+          <t>803974</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>568218</t>
+          <t>566155</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>623617</t>
+          <t>624421</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1318442</t>
+          <t>1320394</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1406484</t>
+          <t>1408145</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>116145</t>
+          <t>118581</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>165057</t>
+          <t>166267</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>103886</t>
+          <t>101205</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>142982</t>
+          <t>144510</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>234517</t>
+          <t>232569</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>295479</t>
+          <t>293451</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24B-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P24B-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24489</t>
+          <t>24027</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45003</t>
+          <t>44658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26015</t>
+          <t>26031</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39217</t>
+          <t>37918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63052</t>
+          <t>63594</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91481</t>
+          <t>91058</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114684</t>
+          <t>114612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46162</t>
+          <t>45686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64544</t>
+          <t>64236</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>146339</t>
+          <t>144714</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>174152</t>
+          <t>175319</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,89%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>24156</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27677</t>
+          <t>27870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44375</t>
+          <t>44851</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15376</t>
+          <t>16885</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34893</t>
+          <t>35656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20812</t>
+          <t>20924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>41227</t>
+          <t>41321</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43437</t>
+          <t>41815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>71250</t>
+          <t>69269</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>25,83%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>79265</t>
+          <t>78708</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>102075</t>
+          <t>101457</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>72109</t>
+          <t>70116</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94322</t>
+          <t>94976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>157728</t>
+          <t>157329</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>189903</t>
+          <t>189336</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>70,6%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11682</t>
+          <t>12396</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27957</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28394</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26365</t>
+          <t>27741</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49898</t>
+          <t>50815</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24214</t>
+          <t>23383</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44955</t>
+          <t>45086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>8010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20166</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36030</t>
+          <t>35509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60343</t>
+          <t>61043</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>170050</t>
+          <t>170314</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199119</t>
+          <t>198290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>16436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>30486</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>192826</t>
+          <t>191026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223817</t>
+          <t>224353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25751</t>
+          <t>25468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47999</t>
+          <t>47960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>33914</t>
+          <t>33641</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58479</t>
+          <t>58733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70499</t>
+          <t>69945</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>104292</t>
+          <t>104584</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38328</t>
+          <t>39387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65367</t>
+          <t>64713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>115480</t>
+          <t>116748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158322</t>
+          <t>157665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>378232</t>
+          <t>381170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>424092</t>
+          <t>425104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>123621</t>
+          <t>123658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155377</t>
+          <t>153377</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>513722</t>
+          <t>514846</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569037</t>
+          <t>570421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59981</t>
+          <t>60307</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>93017</t>
+          <t>91928</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>38871</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>63965</t>
+          <t>63140</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>106713</t>
+          <t>105577</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149159</t>
+          <t>146721</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>20394</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42315</t>
+          <t>41431</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17446</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37445</t>
+          <t>37276</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44227</t>
+          <t>42114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72884</t>
+          <t>71777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>120580</t>
+          <t>122756</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>146361</t>
+          <t>147267</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>107709</t>
+          <t>106448</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>132301</t>
+          <t>133202</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>237108</t>
+          <t>238552</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>273908</t>
+          <t>274330</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31577</t>
+          <t>31404</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>23599</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45064</t>
+          <t>46480</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40556</t>
+          <t>40980</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>68216</t>
+          <t>68686</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>12710</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>14252</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31274</t>
+          <t>31395</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3062,12 +3062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3082,12 +3082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39351</t>
+          <t>39880</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3097,12 +3097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43617</t>
+          <t>42602</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>61326</t>
+          <t>61030</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>90003</t>
+          <t>91429</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>114551</t>
+          <t>114435</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>138710</t>
+          <t>139025</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>170713</t>
+          <t>169616</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,03%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19983</t>
+          <t>20738</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37392</t>
+          <t>38952</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33830</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56042</t>
+          <t>55122</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>58891</t>
+          <t>59417</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>86512</t>
+          <t>88745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>189450</t>
+          <t>188150</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>244133</t>
+          <t>243800</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>135473</t>
+          <t>136444</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>183836</t>
+          <t>181901</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>340594</t>
+          <t>341379</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>413167</t>
+          <t>414018</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>941192</t>
+          <t>936008</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1005927</t>
+          <t>1006826</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>72,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>496802</t>
+          <t>499458</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>553683</t>
+          <t>557452</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1451520</t>
+          <t>1452518</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1539884</t>
+          <t>1540772</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,72%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>168086</t>
+          <t>166890</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>220344</t>
+          <t>218088</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>153789</t>
+          <t>153605</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>200599</t>
+          <t>201581</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>335761</t>
+          <t>337821</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>403272</t>
+          <t>405058</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42479</t>
+          <t>41456</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67371</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22335</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42271</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68979</t>
+          <t>70776</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>99942</t>
+          <t>103138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,73%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62618</t>
+          <t>62595</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86910</t>
+          <t>87669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43601</t>
+          <t>44823</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64977</t>
+          <t>65509</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114719</t>
+          <t>114009</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147052</t>
+          <t>147038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>46,41%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,48%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>10925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28925</t>
+          <t>29607</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19832</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21365</t>
+          <t>20910</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44401</t>
+          <t>43680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>31450</t>
+          <t>31564</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>57045</t>
+          <t>57631</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>26021</t>
+          <t>26998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47053</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64773</t>
+          <t>65263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>97182</t>
+          <t>97783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61658</t>
+          <t>63060</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88354</t>
+          <t>89356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48566</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71977</t>
+          <t>72936</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>117676</t>
+          <t>118120</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>152301</t>
+          <t>154327</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,88%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21364</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43176</t>
+          <t>43771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19466</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40042</t>
+          <t>40044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47230</t>
+          <t>45957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79260</t>
+          <t>77339</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69138</t>
+          <t>69353</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>101768</t>
+          <t>102274</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,82 +5085,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>25,41%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>37,48%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>25179</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>17379</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>33802</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>29,54%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>20,39%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>39,65%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>109328</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>90752</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>130520</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>30,53%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>25,34%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>37,29%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>25179</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>16707</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>33911</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>29,54%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>19,6%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>39,78%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>109328</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>92856</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>129454</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>25,93%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123866</t>
+          <t>122242</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>159036</t>
+          <t>158039</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>39667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56796</t>
+          <t>56864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169826</t>
+          <t>169804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208424</t>
+          <t>209005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>58,36%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35892</t>
+          <t>35446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>60516</t>
+          <t>62067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7056</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20861</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>45314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74707</t>
+          <t>74316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132236</t>
+          <t>128882</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173915</t>
+          <t>173468</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63357</t>
+          <t>62088</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95014</t>
+          <t>95975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>206630</t>
+          <t>205958</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>257849</t>
+          <t>256040</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,65%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>258720</t>
+          <t>258345</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>303713</t>
+          <t>305966</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>131603</t>
+          <t>131573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165375</t>
+          <t>168114</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>401593</t>
+          <t>400297</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>458661</t>
+          <t>458817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,5%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50942</t>
+          <t>50082</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81951</t>
+          <t>80626</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44325</t>
+          <t>43380</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71820</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102375</t>
+          <t>103607</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>145518</t>
+          <t>145434</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44127</t>
+          <t>43646</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70178</t>
+          <t>70104</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>41791</t>
+          <t>42608</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67747</t>
+          <t>69752</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>91547</t>
+          <t>93719</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129814</t>
+          <t>132863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>108640</t>
+          <t>109247</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>137487</t>
+          <t>138857</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>49,73%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>93436</t>
+          <t>92534</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>123702</t>
+          <t>121800</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>209250</t>
+          <t>206989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>251792</t>
+          <t>250346</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,69%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28185</t>
+          <t>28074</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50615</t>
+          <t>50916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39687</t>
+          <t>40202</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65859</t>
+          <t>67764</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>76454</t>
+          <t>76679</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110149</t>
+          <t>110369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>22322</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>21218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>41296</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>32836</t>
+          <t>32382</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>56995</t>
+          <t>57414</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -6551,12 +6551,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26005</t>
+          <t>25253</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>40863</t>
+          <t>41513</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6566,12 +6566,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75994</t>
+          <t>78013</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103653</t>
+          <t>103808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>47,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108153</t>
+          <t>108980</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>139401</t>
+          <t>138441</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,06%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>9068</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23030</t>
+          <t>23861</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32524</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>55185</t>
+          <t>56945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46300</t>
+          <t>45845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72984</t>
+          <t>73304</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>370298</t>
+          <t>371849</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>443590</t>
+          <t>444069</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>230258</t>
+          <t>230384</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>287202</t>
+          <t>286772</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>618624</t>
+          <t>617603</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>710433</t>
+          <t>705153</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>693166</t>
+          <t>693672</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>770103</t>
+          <t>766020</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>475854</t>
+          <t>477791</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>543870</t>
+          <t>542151</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1187922</t>
+          <t>1196797</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1289585</t>
+          <t>1292115</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>190259</t>
+          <t>189828</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>245319</t>
+          <t>245772</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>182675</t>
+          <t>180679</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>234323</t>
+          <t>234804</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>382486</t>
+          <t>383595</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>459674</t>
+          <t>460410</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>18696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37685</t>
+          <t>37134</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24837</t>
+          <t>25541</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33460</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57227</t>
+          <t>56844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57291</t>
+          <t>57896</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>78081</t>
+          <t>78435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34476</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>49432</t>
+          <t>49606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97985</t>
+          <t>97454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>123049</t>
+          <t>124883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4714</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18425</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25215</t>
+          <t>24908</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>15554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>32423</t>
+          <t>32881</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32487</t>
+          <t>32977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35150</t>
+          <t>34427</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60289</t>
+          <t>60228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61486</t>
+          <t>59318</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80908</t>
+          <t>79713</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>52593</t>
+          <t>50890</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71622</t>
+          <t>71115</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>118826</t>
+          <t>118535</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>146351</t>
+          <t>146939</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,14%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16910</t>
+          <t>18385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>22221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>15796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35164</t>
+          <t>34244</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,81%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25685</t>
+          <t>24721</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48456</t>
+          <t>48106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>24055</t>
+          <t>23209</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40391</t>
+          <t>39531</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>65823</t>
+          <t>68293</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135010</t>
+          <t>134807</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163477</t>
+          <t>162764</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,88%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20164</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34934</t>
+          <t>34657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160355</t>
+          <t>159013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>190137</t>
+          <t>190986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20129</t>
+          <t>19659</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41957</t>
+          <t>42171</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4726</t>
+          <t>4160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15558</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>27782</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50432</t>
+          <t>51858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8807,12 +8807,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>86414</t>
+          <t>88045</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121357</t>
+          <t>125445</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58684</t>
+          <t>60536</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88906</t>
+          <t>89010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9002,12 +9002,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155604</t>
+          <t>153030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>204326</t>
+          <t>200633</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>254979</t>
+          <t>253298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>295585</t>
+          <t>294062</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178705</t>
+          <t>178722</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>214199</t>
+          <t>212274</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>445651</t>
+          <t>444865</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>499503</t>
+          <t>499798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>35416</t>
+          <t>35903</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62335</t>
+          <t>63238</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32915</t>
+          <t>33273</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58670</t>
+          <t>59249</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75051</t>
+          <t>75013</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>111965</t>
+          <t>110992</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43765</t>
+          <t>42619</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72586</t>
+          <t>69750</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30738</t>
+          <t>30007</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53602</t>
+          <t>54529</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80948</t>
+          <t>80952</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>114188</t>
+          <t>116538</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>140219</t>
+          <t>140377</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>171604</t>
+          <t>170031</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>136720</t>
+          <t>136907</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>164270</t>
+          <t>163547</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>287596</t>
+          <t>286173</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>328433</t>
+          <t>325914</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,56%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41150</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14363</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32266</t>
+          <t>31707</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>37170</t>
+          <t>38379</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65690</t>
+          <t>64885</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16385</t>
+          <t>16772</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19641</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>38537</t>
+          <t>39223</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27330</t>
+          <t>26885</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>49756</t>
+          <t>50364</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40644</t>
+          <t>39044</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56225</t>
+          <t>55775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>102733</t>
+          <t>102222</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127225</t>
+          <t>126885</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>147749</t>
+          <t>147252</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>177152</t>
+          <t>177118</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -10090,12 +10090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>8251</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>21971</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17998</t>
+          <t>18075</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38953</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30194</t>
+          <t>30839</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53302</t>
+          <t>54198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>228647</t>
+          <t>225613</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>287680</t>
+          <t>285281</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>175165</t>
+          <t>174032</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>223493</t>
+          <t>226002</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>416563</t>
+          <t>414657</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>492024</t>
+          <t>491497</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>736715</t>
+          <t>738534</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>803974</t>
+          <t>803792</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>566155</t>
+          <t>568299</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>624421</t>
+          <t>627045</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1320394</t>
+          <t>1321374</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1408145</t>
+          <t>1411228</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,8%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>118581</t>
+          <t>119128</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>166267</t>
+          <t>163514</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>101205</t>
+          <t>103362</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>144510</t>
+          <t>145935</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>232569</t>
+          <t>233244</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>293451</t>
+          <t>293600</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
